--- a/tiflow-bfarm/main/2.0.0-ballot.2/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/main/2.0.0-ballot.2/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:35:06+00:00</t>
+    <t>2026-07-23T13:18:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
